--- a/CSE-Cdetails.xlsx
+++ b/CSE-Cdetails.xlsx
@@ -425,155 +425,281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>reg id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>collage</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>phone Number</t>
+          <t>attendence</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>24FH1A05F5</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>venkat</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>KVSRIT</t>
-        </is>
+      <c r="C2" t="n">
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>6304256292</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sadiq</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>20</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ST.Joseph</t>
-        </is>
+          <t>24FH1A05H3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>suhail</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>9494141891</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>suhail</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>20</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>KVSRIT</t>
-        </is>
+          <t>24FH1A05I8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>jahash</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>6304667801</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>jahash</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>20</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>KVSRIT</t>
-        </is>
+          <t>24FH1A05J6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>shiva</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>8639917686</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>shiva</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>20</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>KVSRIT</t>
-        </is>
+          <t>24FH1A05H8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>bansi</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>6305153274</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>24FH1A05G8</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Vardhan</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>20</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>KVSRIT</t>
-        </is>
+      <c r="C7" t="n">
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>8074764478</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>24FH1A05J6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>khaiser</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>KVSRIT</t>
-        </is>
+      <c r="C8" t="n">
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>8919821748</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>24FH1A05G1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mahesh</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>24FH1A05F7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sethu sai</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>24FH1A05F3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sai teja</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>24FH1A05H0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>affan</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>24FH1A05I9</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>junaid</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>24FH1A05F4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>govardhan</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>24FH1A05F6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>kishore</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/CSE-Cdetails.xlsx
+++ b/CSE-Cdetails.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,11 +444,6 @@
           <t>age</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>attendence</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -464,9 +459,6 @@
       <c r="C2" t="n">
         <v>20</v>
       </c>
-      <c r="D2" t="n">
-        <v>85</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -482,9 +474,6 @@
       <c r="C3" t="n">
         <v>20</v>
       </c>
-      <c r="D3" t="n">
-        <v>84</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -500,9 +489,6 @@
       <c r="C4" t="n">
         <v>20</v>
       </c>
-      <c r="D4" t="n">
-        <v>90</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,9 +504,6 @@
       <c r="C5" t="n">
         <v>20</v>
       </c>
-      <c r="D5" t="n">
-        <v>78</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -536,9 +519,6 @@
       <c r="C6" t="n">
         <v>20</v>
       </c>
-      <c r="D6" t="n">
-        <v>75</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -554,9 +534,6 @@
       <c r="C7" t="n">
         <v>20</v>
       </c>
-      <c r="D7" t="n">
-        <v>88</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -572,9 +549,6 @@
       <c r="C8" t="n">
         <v>20</v>
       </c>
-      <c r="D8" t="n">
-        <v>70</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -590,9 +564,6 @@
       <c r="C9" t="n">
         <v>20</v>
       </c>
-      <c r="D9" t="n">
-        <v>58</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -608,9 +579,6 @@
       <c r="C10" t="n">
         <v>20</v>
       </c>
-      <c r="D10" t="n">
-        <v>60</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -626,9 +594,6 @@
       <c r="C11" t="n">
         <v>20</v>
       </c>
-      <c r="D11" t="n">
-        <v>74</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -644,9 +609,6 @@
       <c r="C12" t="n">
         <v>20</v>
       </c>
-      <c r="D12" t="n">
-        <v>78</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -662,9 +624,6 @@
       <c r="C13" t="n">
         <v>20</v>
       </c>
-      <c r="D13" t="n">
-        <v>74</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -680,9 +639,6 @@
       <c r="C14" t="n">
         <v>20</v>
       </c>
-      <c r="D14" t="n">
-        <v>68</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -697,9 +653,6 @@
       </c>
       <c r="C15" t="n">
         <v>20</v>
-      </c>
-      <c r="D15" t="n">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
